--- a/Team-Data/2013-14/12-27-2013-14.xlsx
+++ b/Team-Data/2013-14/12-27-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>10</v>
@@ -754,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="AI2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ2" t="n">
         <v>16</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
         <v>22</v>
@@ -793,19 +860,19 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -921,13 +988,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG3" t="n">
         <v>21</v>
@@ -942,7 +1009,7 @@
         <v>26</v>
       </c>
       <c r="AK3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL3" t="n">
         <v>25</v>
@@ -975,19 +1042,19 @@
         <v>30</v>
       </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
         <v>27</v>
       </c>
       <c r="AX3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>19</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
       </c>
       <c r="BA3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
         <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>0.345</v>
+        <v>0.321</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1049,19 +1116,19 @@
         <v>0.444</v>
       </c>
       <c r="L4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M4" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0.372</v>
+        <v>0.368</v>
       </c>
       <c r="O4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="P4" t="n">
-        <v>26.7</v>
+        <v>26.5</v>
       </c>
       <c r="Q4" t="n">
         <v>0.758</v>
@@ -1070,16 +1137,16 @@
         <v>9.699999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>31</v>
+        <v>30.6</v>
       </c>
       <c r="T4" t="n">
-        <v>40.7</v>
+        <v>40.4</v>
       </c>
       <c r="U4" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="W4" t="n">
         <v>6.8</v>
@@ -1088,25 +1155,25 @@
         <v>4.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z4" t="n">
         <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.8</v>
+        <v>-5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
         <v>24</v>
@@ -1115,7 +1182,7 @@
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1124,16 +1191,16 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AM4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
         <v>5</v>
@@ -1142,13 +1209,13 @@
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
         <v>28</v>
@@ -1157,7 +1224,7 @@
         <v>21</v>
       </c>
       <c r="AV4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
         <v>26</v>
@@ -1166,13 +1233,13 @@
         <v>27</v>
       </c>
       <c r="AY4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ4" t="n">
         <v>25</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
         <v>21</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -1207,49 +1274,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" t="n">
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.467</v>
+        <v>0.483</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
       </c>
       <c r="I5" t="n">
-        <v>34.5</v>
+        <v>34.6</v>
       </c>
       <c r="J5" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.422</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M5" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="N5" t="n">
-        <v>0.317</v>
+        <v>0.313</v>
       </c>
       <c r="O5" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P5" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.719</v>
+        <v>0.717</v>
       </c>
       <c r="R5" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S5" t="n">
         <v>32.6</v>
@@ -1258,7 +1325,7 @@
         <v>43.3</v>
       </c>
       <c r="U5" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="V5" t="n">
         <v>13.4</v>
@@ -1276,28 +1343,28 @@
         <v>19.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>92.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.2</v>
+        <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>12</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI5" t="n">
         <v>29</v>
@@ -1318,16 +1385,16 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AP5" t="n">
         <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
         <v>13</v>
@@ -1339,10 +1406,10 @@
         <v>26</v>
       </c>
       <c r="AV5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX5" t="n">
         <v>8</v>
@@ -1351,16 +1418,16 @@
         <v>25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
         <v>29</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -1467,19 +1534,19 @@
         <v>-0.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
         <v>22</v>
       </c>
       <c r="AH6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1500,7 +1567,7 @@
         <v>27</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1509,7 +1576,7 @@
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1524,7 +1591,7 @@
         <v>27</v>
       </c>
       <c r="AW6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX6" t="n">
         <v>14</v>
@@ -1533,7 +1600,7 @@
         <v>30</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA6" t="n">
         <v>9</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-6</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -1664,31 +1731,31 @@
         <v>4</v>
       </c>
       <c r="AI7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK7" t="n">
         <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO7" t="n">
         <v>21</v>
       </c>
       <c r="AP7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR7" t="n">
         <v>8</v>
@@ -1709,16 +1776,16 @@
         <v>19</v>
       </c>
       <c r="AX7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
         <v>23</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1861,7 +1928,7 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
@@ -1876,13 +1943,13 @@
         <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>27</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -1935,43 +2002,43 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E9" t="n">
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.519</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="J9" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L9" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M9" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0.344</v>
+        <v>0.347</v>
       </c>
       <c r="O9" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P9" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0.722</v>
@@ -1980,46 +2047,46 @@
         <v>12.9</v>
       </c>
       <c r="S9" t="n">
-        <v>33.6</v>
+        <v>33.7</v>
       </c>
       <c r="T9" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="U9" t="n">
         <v>21.3</v>
       </c>
       <c r="V9" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W9" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X9" t="n">
         <v>5.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="AA9" t="n">
         <v>21.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.1</v>
+        <v>100.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AG9" t="n">
         <v>12</v>
@@ -2034,19 +2101,19 @@
         <v>7</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
         <v>19</v>
       </c>
       <c r="AM9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
         <v>7</v>
@@ -2058,13 +2125,13 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
         <v>13</v>
@@ -2079,16 +2146,16 @@
         <v>28</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
         <v>15</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.452</v>
+        <v>0.467</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
@@ -2135,94 +2202,94 @@
         <v>38.9</v>
       </c>
       <c r="J10" t="n">
-        <v>86.2</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L10" t="n">
         <v>6.4</v>
       </c>
       <c r="M10" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="O10" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="P10" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.666</v>
+        <v>0.67</v>
       </c>
       <c r="R10" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T10" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U10" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V10" t="n">
         <v>15.2</v>
       </c>
       <c r="W10" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X10" t="n">
         <v>5.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA10" t="n">
         <v>20.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.5</v>
+        <v>100.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.4</v>
+        <v>-0.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>12</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AN10" t="n">
         <v>29</v>
@@ -2231,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
         <v>30</v>
@@ -2246,13 +2313,13 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="n">
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -2299,85 +2366,85 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.581</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="J11" t="n">
-        <v>83.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.462</v>
+        <v>0.459</v>
       </c>
       <c r="L11" t="n">
         <v>9.5</v>
       </c>
       <c r="M11" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="N11" t="n">
         <v>0.403</v>
       </c>
       <c r="O11" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="P11" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.727</v>
+        <v>0.728</v>
       </c>
       <c r="R11" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S11" t="n">
-        <v>35</v>
+        <v>34.8</v>
       </c>
       <c r="T11" t="n">
-        <v>46.2</v>
+        <v>45.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="V11" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="W11" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>103</v>
+        <v>102.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,22 +2456,22 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
         <v>10</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AK11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL11" t="n">
         <v>3</v>
       </c>
       <c r="AM11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2413,19 +2480,19 @@
         <v>20</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11" t="n">
         <v>24</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -2440,19 +2507,19 @@
         <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ11" t="n">
         <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -2559,13 +2626,13 @@
         <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG12" t="n">
         <v>6</v>
@@ -2592,7 +2659,7 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2619,19 +2686,19 @@
         <v>17</v>
       </c>
       <c r="AX12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
         <v>24</v>
@@ -2765,19 +2832,19 @@
         <v>10</v>
       </c>
       <c r="AL13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AM13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2795,7 +2862,7 @@
         <v>18</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>18</v>
@@ -2804,10 +2871,10 @@
         <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>5.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
         <v>6</v>
@@ -2941,7 +3008,7 @@
         <v>11</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="n">
         <v>7</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
@@ -2971,7 +3038,7 @@
         <v>12</v>
       </c>
       <c r="AT14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU14" t="n">
         <v>5</v>
@@ -2980,10 +3047,10 @@
         <v>5</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" t="n">
         <v>13</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.433</v>
+        <v>0.448</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L15" t="n">
         <v>9.4</v>
@@ -3057,31 +3124,31 @@
         <v>25.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.374</v>
+        <v>0.376</v>
       </c>
       <c r="O15" t="n">
         <v>16.1</v>
       </c>
       <c r="P15" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.731</v>
+        <v>0.732</v>
       </c>
       <c r="R15" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T15" t="n">
-        <v>42.7</v>
+        <v>42.9</v>
       </c>
       <c r="U15" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="V15" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
         <v>6.9</v>
@@ -3096,25 +3163,25 @@
         <v>20.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC15" t="n">
         <v>-4</v>
       </c>
       <c r="AD15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH15" t="n">
         <v>27</v>
@@ -3123,10 +3190,10 @@
         <v>17</v>
       </c>
       <c r="AJ15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
@@ -3141,7 +3208,7 @@
         <v>19</v>
       </c>
       <c r="AP15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
         <v>23</v>
@@ -3153,10 +3220,10 @@
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV15" t="n">
         <v>15</v>
@@ -3168,13 +3235,13 @@
         <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -3287,25 +3354,25 @@
         <v>-3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF16" t="n">
         <v>18</v>
       </c>
-      <c r="AF16" t="n">
-        <v>17</v>
-      </c>
       <c r="AG16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH16" t="n">
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK16" t="n">
         <v>15</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
@@ -3326,19 +3393,19 @@
         <v>27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR16" t="n">
         <v>10</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3350,7 +3417,7 @@
         <v>28</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -3391,55 +3458,55 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17" t="n">
         <v>22</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.759</v>
+        <v>0.786</v>
       </c>
       <c r="H17" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I17" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="J17" t="n">
-        <v>76.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.511</v>
+        <v>0.514</v>
       </c>
       <c r="L17" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="N17" t="n">
-        <v>0.377</v>
+        <v>0.379</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.755</v>
+        <v>0.754</v>
       </c>
       <c r="R17" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="S17" t="n">
         <v>29.9</v>
       </c>
       <c r="T17" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="U17" t="n">
         <v>24.1</v>
@@ -3454,10 +3521,10 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA17" t="n">
         <v>21.2</v>
@@ -3466,10 +3533,10 @@
         <v>104.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3478,13 +3545,13 @@
         <v>4</v>
       </c>
       <c r="AG17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI17" t="n">
         <v>5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3493,13 +3560,13 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO17" t="n">
         <v>12</v>
@@ -3508,7 +3575,7 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,19 +3590,19 @@
         <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -3573,73 +3640,73 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" t="n">
         <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>0.207</v>
+        <v>0.214</v>
       </c>
       <c r="H18" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="I18" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J18" t="n">
-        <v>82.7</v>
+        <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.419</v>
+        <v>0.421</v>
       </c>
       <c r="L18" t="n">
         <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.352</v>
+        <v>0.356</v>
       </c>
       <c r="O18" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="P18" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="R18" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S18" t="n">
         <v>30.3</v>
       </c>
       <c r="T18" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
         <v>20.6</v>
       </c>
       <c r="V18" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="W18" t="n">
         <v>6.9</v>
       </c>
       <c r="X18" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AA18" t="n">
         <v>20.4</v>
@@ -3648,10 +3715,10 @@
         <v>92.59999999999999</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.8</v>
+        <v>-7.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3663,7 +3730,7 @@
         <v>30</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>28</v>
@@ -3678,16 +3745,16 @@
         <v>20</v>
       </c>
       <c r="AM18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>18</v>
       </c>
       <c r="AP18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ18" t="n">
         <v>6</v>
@@ -3696,16 +3763,16 @@
         <v>16</v>
       </c>
       <c r="AS18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
@@ -3717,10 +3784,10 @@
         <v>18</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
         <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>0.483</v>
+        <v>0.464</v>
       </c>
       <c r="H19" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J19" t="n">
-        <v>89.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="K19" t="n">
-        <v>0.427</v>
+        <v>0.425</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="N19" t="n">
         <v>0.334</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.4</v>
       </c>
       <c r="P19" t="n">
-        <v>27.3</v>
+        <v>26.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.798</v>
+        <v>0.797</v>
       </c>
       <c r="R19" t="n">
         <v>13.9</v>
       </c>
       <c r="S19" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T19" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U19" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V19" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="W19" t="n">
         <v>9.1</v>
@@ -3818,37 +3885,37 @@
         <v>2.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.1</v>
+        <v>105.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AF19" t="n">
         <v>15</v>
       </c>
       <c r="AG19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI19" t="n">
         <v>13</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>12</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -3860,13 +3927,13 @@
         <v>13</v>
       </c>
       <c r="AM19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN19" t="n">
         <v>26</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3881,13 +3948,13 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
         <v>3</v>
@@ -3896,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
         <v>1</v>
@@ -3905,10 +3972,10 @@
         <v>3</v>
       </c>
       <c r="BB19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -3937,61 +4004,61 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>0.481</v>
+        <v>0.462</v>
       </c>
       <c r="H20" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I20" t="n">
-        <v>39.2</v>
+        <v>39.1</v>
       </c>
       <c r="J20" t="n">
         <v>87.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.388</v>
+        <v>0.384</v>
       </c>
       <c r="O20" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="P20" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R20" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T20" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="U20" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="V20" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="W20" t="n">
         <v>9</v>
@@ -4000,37 +4067,37 @@
         <v>6.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
         <v>21.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>102.9</v>
+        <v>102.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AH20" t="n">
         <v>6</v>
       </c>
       <c r="AI20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ20" t="n">
         <v>4</v>
@@ -4045,13 +4112,13 @@
         <v>27</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
         <v>13</v>
       </c>
       <c r="AP20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
@@ -4060,37 +4127,37 @@
         <v>3</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW20" t="n">
         <v>4</v>
       </c>
       <c r="AX20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>27</v>
       </c>
       <c r="AZ20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" t="n">
         <v>9</v>
       </c>
       <c r="F21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>0.31</v>
+        <v>0.321</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>35.8</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.428</v>
+        <v>0.43</v>
       </c>
       <c r="L21" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.354</v>
+        <v>0.349</v>
       </c>
       <c r="O21" t="n">
         <v>14</v>
@@ -4158,64 +4225,64 @@
         <v>18.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.763</v>
+        <v>0.769</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S21" t="n">
         <v>28.5</v>
       </c>
       <c r="T21" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="U21" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V21" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W21" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y21" t="n">
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="AA21" t="n">
         <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-4.2</v>
+        <v>-3.9</v>
       </c>
       <c r="AD21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH21" t="n">
         <v>9</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>10</v>
       </c>
       <c r="AI21" t="n">
         <v>25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK21" t="n">
         <v>25</v>
@@ -4227,7 +4294,7 @@
         <v>4</v>
       </c>
       <c r="AN21" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4239,7 +4306,7 @@
         <v>11</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
         <v>30</v>
@@ -4248,31 +4315,31 @@
         <v>29</v>
       </c>
       <c r="AU21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY21" t="n">
         <v>7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB21" t="n">
         <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -4301,100 +4368,100 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
         <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.828</v>
+        <v>0.821</v>
       </c>
       <c r="H22" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.467</v>
+        <v>0.469</v>
       </c>
       <c r="L22" t="n">
         <v>6.8</v>
       </c>
       <c r="M22" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0.349</v>
+        <v>0.351</v>
       </c>
       <c r="O22" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="P22" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.824</v>
       </c>
       <c r="R22" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S22" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="T22" t="n">
         <v>47.3</v>
       </c>
       <c r="U22" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="V22" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W22" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X22" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.7</v>
+        <v>106.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ22" t="n">
         <v>15</v>
@@ -4409,7 +4476,7 @@
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO22" t="n">
         <v>3</v>
@@ -4418,10 +4485,10 @@
         <v>5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
         <v>1</v>
@@ -4430,10 +4497,10 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
         <v>13</v>
@@ -4445,13 +4512,13 @@
         <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="n">
         <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>0.31</v>
+        <v>0.286</v>
       </c>
       <c r="H23" t="n">
         <v>48.5</v>
       </c>
       <c r="I23" t="n">
-        <v>36.9</v>
+        <v>36.6</v>
       </c>
       <c r="J23" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.446</v>
+        <v>0.443</v>
       </c>
       <c r="L23" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="M23" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O23" t="n">
         <v>15.8</v>
@@ -4522,28 +4589,28 @@
         <v>20.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.755</v>
+        <v>0.759</v>
       </c>
       <c r="R23" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S23" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U23" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V23" t="n">
         <v>15.5</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y23" t="n">
         <v>5.9</v>
@@ -4552,43 +4619,43 @@
         <v>20.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>97</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-3.5</v>
+        <v>-4.2</v>
       </c>
       <c r="AD23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AH23" t="n">
         <v>9</v>
       </c>
-      <c r="AE23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>10</v>
-      </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>18</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM23" t="n">
         <v>15</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>16</v>
       </c>
       <c r="AN23" t="n">
         <v>13</v>
@@ -4600,19 +4667,19 @@
         <v>24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4621,7 +4688,7 @@
         <v>16</v>
       </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY23" t="n">
         <v>24</v>
@@ -4630,13 +4697,13 @@
         <v>15</v>
       </c>
       <c r="BA23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
         <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH24" t="n">
         <v>1</v>
@@ -4767,7 +4834,7 @@
         <v>16</v>
       </c>
       <c r="AL24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AM24" t="n">
         <v>10</v>
@@ -4788,13 +4855,13 @@
         <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT24" t="n">
         <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4809,7 +4876,7 @@
         <v>29</v>
       </c>
       <c r="AZ24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA24" t="n">
         <v>20</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -4847,67 +4914,67 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
         <v>17</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
-        <v>0.607</v>
+        <v>0.63</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="J25" t="n">
-        <v>82.5</v>
+        <v>82.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>0.464</v>
       </c>
       <c r="L25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.377</v>
+        <v>0.384</v>
       </c>
       <c r="O25" t="n">
         <v>17.6</v>
       </c>
       <c r="P25" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.747</v>
+        <v>0.745</v>
       </c>
       <c r="R25" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="S25" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T25" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U25" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="V25" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W25" t="n">
         <v>8.4</v>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
@@ -4916,19 +4983,19 @@
         <v>21.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.2</v>
+        <v>103.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="n">
         <v>6</v>
@@ -4937,16 +5004,16 @@
         <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL25" t="n">
         <v>2</v>
@@ -4955,7 +5022,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO25" t="n">
         <v>15</v>
@@ -4967,7 +5034,7 @@
         <v>21</v>
       </c>
       <c r="AR25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4976,13 +5043,13 @@
         <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV25" t="n">
         <v>23</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX25" t="n">
         <v>10</v>
@@ -4994,13 +5061,13 @@
         <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BB25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>6.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5119,7 +5186,7 @@
         <v>1</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
@@ -5140,19 +5207,19 @@
         <v>2</v>
       </c>
       <c r="AO26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP26" t="n">
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR26" t="n">
         <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
         <v>3</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -5211,100 +5278,100 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="n">
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.321</v>
+        <v>0.296</v>
       </c>
       <c r="H27" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J27" t="n">
         <v>83</v>
       </c>
       <c r="K27" t="n">
-        <v>0.443</v>
+        <v>0.441</v>
       </c>
       <c r="L27" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
         <v>20.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="O27" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P27" t="n">
         <v>25.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.775</v>
+        <v>0.773</v>
       </c>
       <c r="R27" t="n">
         <v>11.3</v>
       </c>
       <c r="S27" t="n">
-        <v>30.9</v>
+        <v>30.5</v>
       </c>
       <c r="T27" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="U27" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V27" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="W27" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X27" t="n">
         <v>3.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA27" t="n">
         <v>22.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-3.6</v>
+        <v>-4</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>17</v>
@@ -5334,19 +5401,19 @@
         <v>12</v>
       </c>
       <c r="AS27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
         <v>22</v>
       </c>
       <c r="AU27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV27" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -5471,16 +5538,16 @@
         <v>7.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH28" t="n">
         <v>27</v>
@@ -5489,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5504,7 +5571,7 @@
         <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP28" t="n">
         <v>29</v>
@@ -5516,10 +5583,10 @@
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5531,7 +5598,7 @@
         <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -5575,64 +5642,64 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F29" t="n">
         <v>15</v>
       </c>
       <c r="G29" t="n">
-        <v>0.444</v>
+        <v>0.423</v>
       </c>
       <c r="H29" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I29" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>83.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L29" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M29" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="N29" t="n">
         <v>0.342</v>
       </c>
       <c r="O29" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P29" t="n">
-        <v>24.9</v>
+        <v>24.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.777</v>
+        <v>0.781</v>
       </c>
       <c r="R29" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S29" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T29" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="U29" t="n">
         <v>18.7</v>
       </c>
       <c r="V29" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X29" t="n">
         <v>4.6</v>
@@ -5641,28 +5708,28 @@
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AA29" t="n">
         <v>22.4</v>
       </c>
-      <c r="AA29" t="n">
-        <v>22.6</v>
-      </c>
       <c r="AB29" t="n">
-        <v>99.09999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE29" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="n">
         <v>15</v>
       </c>
       <c r="AG29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH29" t="n">
         <v>5</v>
@@ -5677,7 +5744,7 @@
         <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AM29" t="n">
         <v>13</v>
@@ -5689,46 +5756,46 @@
         <v>7</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ29" t="n">
         <v>7</v>
       </c>
       <c r="AR29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT29" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV29" t="n">
         <v>11</v>
       </c>
       <c r="AW29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
       </c>
       <c r="AZ29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
       </c>
       <c r="BB29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -5757,58 +5824,58 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.281</v>
+        <v>0.258</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
       </c>
       <c r="I30" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J30" t="n">
-        <v>82.3</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L30" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M30" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.345</v>
+        <v>0.343</v>
       </c>
       <c r="O30" t="n">
         <v>15.8</v>
       </c>
       <c r="P30" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.754</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
         <v>11.9</v>
       </c>
       <c r="S30" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T30" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="V30" t="n">
         <v>15.4</v>
@@ -5817,43 +5884,43 @@
         <v>7.1</v>
       </c>
       <c r="X30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA30" t="n">
         <v>20.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>93.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-8.5</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AF30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG30" t="n">
         <v>29</v>
       </c>
       <c r="AH30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
       </c>
       <c r="AJ30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK30" t="n">
         <v>24</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
         <v>25</v>
@@ -5874,7 +5941,7 @@
         <v>23</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
@@ -5889,19 +5956,19 @@
         <v>25</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY30" t="n">
         <v>19</v>
       </c>
       <c r="AZ30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
         <v>14</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" t="n">
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31" t="n">
-        <v>0.462</v>
+        <v>0.48</v>
       </c>
       <c r="H31" t="n">
         <v>49.2</v>
@@ -5972,61 +6039,61 @@
         <v>0.392</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P31" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.74</v>
+        <v>0.737</v>
       </c>
       <c r="R31" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
-        <v>31.3</v>
+        <v>31.6</v>
       </c>
       <c r="T31" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
       <c r="U31" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V31" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W31" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.09999999999999</v>
+        <v>99.2</v>
       </c>
       <c r="AC31" t="n">
-        <v>-1.6</v>
+        <v>-0.8</v>
       </c>
       <c r="AD31" t="n">
         <v>30</v>
       </c>
       <c r="AE31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AG31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
         <v>3</v>
@@ -6038,13 +6105,13 @@
         <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL31" t="n">
         <v>8</v>
       </c>
       <c r="AM31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AN31" t="n">
         <v>4</v>
@@ -6053,46 +6120,46 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
         <v>22</v>
       </c>
       <c r="AR31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AS31" t="n">
         <v>18</v>
       </c>
       <c r="AT31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV31" t="n">
         <v>22</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-27-2013-14</t>
+          <t>2013-12-27</t>
         </is>
       </c>
     </row>
